--- a/ClimOO material/materials for implementations/ClimOO Vocabulary.xlsx
+++ b/ClimOO material/materials for implementations/ClimOO Vocabulary.xlsx
@@ -5,18 +5,18 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/f.u./Desktop/ClimOO-Ontology/ClimOO material/materials for implementations /"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/f.u./Desktop/ClimOO-Ontology/ClimOO material/materials for implementations/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1B034F02-DB40-A545-B432-80EF90361BD1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8BF126E2-A2A0-F84F-8C7C-4E74043AA109}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="29520" yWindow="4280" windowWidth="28800" windowHeight="16380" xr2:uid="{CB153552-6711-0040-AB62-F0CB02156726}"/>
+    <workbookView xWindow="34160" yWindow="2640" windowWidth="28800" windowHeight="16420" xr2:uid="{CB153552-6711-0040-AB62-F0CB02156726}"/>
   </bookViews>
   <sheets>
     <sheet name="ClimOO Vocabulary" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'ClimOO Vocabulary'!$A$1:$A$861</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'ClimOO Vocabulary'!$A$1:$A$852</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2613" uniqueCount="868">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3105" uniqueCount="1042">
   <si>
     <t>Terms</t>
   </si>
@@ -2643,6 +2643,528 @@
   </si>
   <si>
     <t>yellow</t>
+  </si>
+  <si>
+    <t>plastic manufacturing process</t>
+  </si>
+  <si>
+    <t>thermoplasticity</t>
+  </si>
+  <si>
+    <t>thermosetting disposition</t>
+  </si>
+  <si>
+    <t>elasticity</t>
+  </si>
+  <si>
+    <t>polymerisation monomer</t>
+  </si>
+  <si>
+    <t>monomer</t>
+  </si>
+  <si>
+    <t>polymer</t>
+  </si>
+  <si>
+    <t>thermosetting polymer</t>
+  </si>
+  <si>
+    <t>thermoplastic polymer</t>
+  </si>
+  <si>
+    <t>elastomer</t>
+  </si>
+  <si>
+    <t>thermoplastic elastomer</t>
+  </si>
+  <si>
+    <t>synthetic polymer</t>
+  </si>
+  <si>
+    <t>inorganic or hybrid polymer</t>
+  </si>
+  <si>
+    <t>copolymer</t>
+  </si>
+  <si>
+    <t>modified natural polymer</t>
+  </si>
+  <si>
+    <t>synthetic copolymer</t>
+  </si>
+  <si>
+    <t>bio-based polymer</t>
+  </si>
+  <si>
+    <t>recyclable polymer</t>
+  </si>
+  <si>
+    <t>recycled polymer</t>
+  </si>
+  <si>
+    <t>biodegradable polymer</t>
+  </si>
+  <si>
+    <t>synthetic polymer-based material additive</t>
+  </si>
+  <si>
+    <t>plastic additive</t>
+  </si>
+  <si>
+    <t>synthetic polymer-based material additive role</t>
+  </si>
+  <si>
+    <t>residue molecule of synthetic polymer manufacturing</t>
+  </si>
+  <si>
+    <t>bio-based plastic</t>
+  </si>
+  <si>
+    <t>recycled plastic</t>
+  </si>
+  <si>
+    <t>recyclable plastic</t>
+  </si>
+  <si>
+    <t>virgin plastic</t>
+  </si>
+  <si>
+    <t>biodegradable plastic</t>
+  </si>
+  <si>
+    <t>synthetic biodegradable plastic</t>
+  </si>
+  <si>
+    <t>synthetic polymer-based material</t>
+  </si>
+  <si>
+    <t>copolymer-based synthetic material</t>
+  </si>
+  <si>
+    <t>polymer composite-based synthetic material</t>
+  </si>
+  <si>
+    <t>inorganic or hybrid polymer-based synthetic material</t>
+  </si>
+  <si>
+    <t>thermoplastic elastomer-based synthetic material</t>
+  </si>
+  <si>
+    <t>usage of some piece of synthetic polymer-based material</t>
+  </si>
+  <si>
+    <t>plastic object usage process</t>
+  </si>
+  <si>
+    <t>piece of biodegradable plastic</t>
+  </si>
+  <si>
+    <t>piece of biodegradable synthetic plastic</t>
+  </si>
+  <si>
+    <t>piece of bio-based plastic</t>
+  </si>
+  <si>
+    <t>piece of recyclable plastic</t>
+  </si>
+  <si>
+    <t>piece of virgin plastic</t>
+  </si>
+  <si>
+    <t>piece of recycled plastic</t>
+  </si>
+  <si>
+    <t>piece of polymer-based synthetic material</t>
+  </si>
+  <si>
+    <t>piece of copolymer-based synthetic material</t>
+  </si>
+  <si>
+    <t>piece of polymer composite-based synthetic material</t>
+  </si>
+  <si>
+    <t>piece of inorganic or hybrid polymer-based synthetic material</t>
+  </si>
+  <si>
+    <t>piece of thermoplastic elastomer-based synthetic material</t>
+  </si>
+  <si>
+    <t>piece of synthetic plastic</t>
+  </si>
+  <si>
+    <t>plastic object</t>
+  </si>
+  <si>
+    <t>biodegradable plastic object</t>
+  </si>
+  <si>
+    <t>bio-based plastic object</t>
+  </si>
+  <si>
+    <t>recyclable plastic object</t>
+  </si>
+  <si>
+    <t>virgin plastic object</t>
+  </si>
+  <si>
+    <t>recycled plastic object</t>
+  </si>
+  <si>
+    <t>agriplastic object</t>
+  </si>
+  <si>
+    <t>macro-particle of plastic</t>
+  </si>
+  <si>
+    <t>mega-particle of plastic</t>
+  </si>
+  <si>
+    <t>meso-particle of plastic</t>
+  </si>
+  <si>
+    <t>micro-particle of plastic</t>
+  </si>
+  <si>
+    <t>nano-particle of plastic</t>
+  </si>
+  <si>
+    <t>plastic debris aggregate</t>
+  </si>
+  <si>
+    <t>plastic debris particle</t>
+  </si>
+  <si>
+    <t>large microplastic debris particle</t>
+  </si>
+  <si>
+    <t>submicron plastic debris particle</t>
+  </si>
+  <si>
+    <t>debris particle of foam</t>
+  </si>
+  <si>
+    <t>film debris particle</t>
+  </si>
+  <si>
+    <t>linear plastic debris particle</t>
+  </si>
+  <si>
+    <t>plastic pellet debris particle</t>
+  </si>
+  <si>
+    <t>plastic surface coating debris particle</t>
+  </si>
+  <si>
+    <t>tire wear particle</t>
+  </si>
+  <si>
+    <t>tire wear and road particle</t>
+  </si>
+  <si>
+    <t>biodegradable - claim</t>
+  </si>
+  <si>
+    <t>biobased - claim</t>
+  </si>
+  <si>
+    <t>recyclable - claim</t>
+  </si>
+  <si>
+    <t>recycled - claim</t>
+  </si>
+  <si>
+    <t>biodegradable composition</t>
+  </si>
+  <si>
+    <t>biobased composition</t>
+  </si>
+  <si>
+    <t>recyclable composition</t>
+  </si>
+  <si>
+    <t>recycled composition</t>
+  </si>
+  <si>
+    <t>recyclability</t>
+  </si>
+  <si>
+    <t>biodegradability</t>
+  </si>
+  <si>
+    <t>environment persistence</t>
+  </si>
+  <si>
+    <t>water solubility</t>
+  </si>
+  <si>
+    <t>plastic debris source</t>
+  </si>
+  <si>
+    <t>plastic debris sink</t>
+  </si>
+  <si>
+    <t>plastic debris source role</t>
+  </si>
+  <si>
+    <t>plastic debris sink role</t>
+  </si>
+  <si>
+    <t>plastic degradation</t>
+  </si>
+  <si>
+    <t>synthetic plastic degradation</t>
+  </si>
+  <si>
+    <t>polymer biodegradation</t>
+  </si>
+  <si>
+    <t>biodegradation of synthetic plastic</t>
+  </si>
+  <si>
+    <t>biodegradation of piece of sythetic plastic</t>
+  </si>
+  <si>
+    <t>plastic debris degradation</t>
+  </si>
+  <si>
+    <t>plastic debris fragmentation</t>
+  </si>
+  <si>
+    <t>plastic fragmentation</t>
+  </si>
+  <si>
+    <t>synthetic plastic fragmentation</t>
+  </si>
+  <si>
+    <t>fragmentation of a piece of synthetic polymer-based material</t>
+  </si>
+  <si>
+    <t>microplastic pollution</t>
+  </si>
+  <si>
+    <t>biodegradable polymer production</t>
+  </si>
+  <si>
+    <t>production process of a piece of synthetic biodegradable plastic</t>
+  </si>
+  <si>
+    <t>biodegradable synthetic plastic production process</t>
+  </si>
+  <si>
+    <t>plastic object manufacturing process</t>
+  </si>
+  <si>
+    <t>bio-based polymer production</t>
+  </si>
+  <si>
+    <t>production process of piece of bio-based plastic</t>
+  </si>
+  <si>
+    <t>bio-based plastic production process</t>
+  </si>
+  <si>
+    <t>production process of a piece of recycled plastic</t>
+  </si>
+  <si>
+    <t>production process of a piece of recyclable plastic</t>
+  </si>
+  <si>
+    <t>recyclable plastic production process</t>
+  </si>
+  <si>
+    <t>recycled plastic production process</t>
+  </si>
+  <si>
+    <t>reclyclable polymer production process</t>
+  </si>
+  <si>
+    <t>synthetic polymer-based material sorption of pollutants</t>
+  </si>
+  <si>
+    <t>plastic sorption of pollutants</t>
+  </si>
+  <si>
+    <t>microplastic sorption of pollutants</t>
+  </si>
+  <si>
+    <t>release of plastic debris-carried pollutants in the environment</t>
+  </si>
+  <si>
+    <t>plastic upcycling process</t>
+  </si>
+  <si>
+    <t>recycling process of synthetic polymers</t>
+  </si>
+  <si>
+    <t>plastic recycling process</t>
+  </si>
+  <si>
+    <t>mineralization process</t>
+  </si>
+  <si>
+    <t>plastic mineralization process</t>
+  </si>
+  <si>
+    <t>synthetic plastic mineralization process</t>
+  </si>
+  <si>
+    <t>plastic biomineralization process</t>
+  </si>
+  <si>
+    <t>pollution prevention</t>
+  </si>
+  <si>
+    <t>plastic combustion</t>
+  </si>
+  <si>
+    <t>ecosystem service</t>
+  </si>
+  <si>
+    <t>compostability</t>
+  </si>
+  <si>
+    <t>composting environment</t>
+  </si>
+  <si>
+    <t>compost</t>
+  </si>
+  <si>
+    <t>composting process</t>
+  </si>
+  <si>
+    <t>plastic composting process</t>
+  </si>
+  <si>
+    <t>compostable synthetic plastic</t>
+  </si>
+  <si>
+    <t>piece of compostable synthetic plastic</t>
+  </si>
+  <si>
+    <t>compostable plastic object</t>
+  </si>
+  <si>
+    <t>analyte role</t>
+  </si>
+  <si>
+    <t>analyte</t>
+  </si>
+  <si>
+    <t>experiment matrix</t>
+  </si>
+  <si>
+    <t>experiment matrix role</t>
+  </si>
+  <si>
+    <t>blank matrix</t>
+  </si>
+  <si>
+    <t>sample</t>
+  </si>
+  <si>
+    <t>experiment process</t>
+  </si>
+  <si>
+    <t>reference material role</t>
+  </si>
+  <si>
+    <t>reference material (RM)</t>
+  </si>
+  <si>
+    <t>internal standard material</t>
+  </si>
+  <si>
+    <t>internal standard role</t>
+  </si>
+  <si>
+    <t>extraction</t>
+  </si>
+  <si>
+    <t>extract</t>
+  </si>
+  <si>
+    <t>analyte extract</t>
+  </si>
+  <si>
+    <t>best available technology</t>
+  </si>
+  <si>
+    <t>certificate scheme</t>
+  </si>
+  <si>
+    <t>debt instrument</t>
+  </si>
+  <si>
+    <t>green debt instrument</t>
+  </si>
+  <si>
+    <t>debt issuer role</t>
+  </si>
+  <si>
+    <t>debt Issuer</t>
+  </si>
+  <si>
+    <t>debt borrower role</t>
+  </si>
+  <si>
+    <t>debt borrower</t>
+  </si>
+  <si>
+    <t>debt lender role</t>
+  </si>
+  <si>
+    <t>debt lender</t>
+  </si>
+  <si>
+    <t>environmental performance value</t>
+  </si>
+  <si>
+    <t>environmental performance indicator</t>
+  </si>
+  <si>
+    <t>environmental performance indicator value</t>
+  </si>
+  <si>
+    <t xml:space="preserve">No yet </t>
+  </si>
+  <si>
+    <t>trasformation process</t>
+  </si>
+  <si>
+    <t>production process of a piece of synthetic plastic</t>
+  </si>
+  <si>
+    <t>synthetic polymer production process</t>
+  </si>
+  <si>
+    <t>transparent</t>
+  </si>
+  <si>
+    <t xml:space="preserve">macroplastic particle - Hartmann et a. (2019) classification </t>
+  </si>
+  <si>
+    <t xml:space="preserve">mesoplastic particle - Hartmann et a. (2019) classification </t>
+  </si>
+  <si>
+    <t xml:space="preserve">microplastic particle - Hartmann et a. (2019) classification </t>
+  </si>
+  <si>
+    <t>synthetic plastic biomineralization process</t>
+  </si>
+  <si>
+    <t>plastic debris sorption of pollutants</t>
+  </si>
+  <si>
+    <t>plastic pollution prevention</t>
+  </si>
+  <si>
+    <t>compostable - claim</t>
+  </si>
+  <si>
+    <t>compostable composition</t>
+  </si>
+  <si>
+    <t xml:space="preserve">disposition to motion in the environment </t>
   </si>
 </sst>
 </file>
@@ -2709,7 +3231,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -2718,11 +3240,22 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normale" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="3">
+  <dxfs count="4">
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -3083,7 +3616,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A05EE52F-6B9B-9646-8D2F-C9D94D87C781}">
-  <dimension ref="A1:D873"/>
+  <dimension ref="A1:D1041"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="82.5" style="1" bestFit="1" customWidth="1"/>
@@ -11299,7 +11832,7 @@
     </row>
     <row r="748" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A748" s="1" t="s">
-        <v>104</v>
+        <v>747</v>
       </c>
       <c r="B748" s="1" t="s">
         <v>421</v>
@@ -11310,7 +11843,7 @@
     </row>
     <row r="749" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A749" s="1" t="s">
-        <v>747</v>
+        <v>745</v>
       </c>
       <c r="B749" s="1" t="s">
         <v>421</v>
@@ -11319,20 +11852,20 @@
         <v>422</v>
       </c>
     </row>
-    <row r="750" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A750" s="1" t="s">
-        <v>745</v>
-      </c>
-      <c r="B750" s="1" t="s">
-        <v>421</v>
-      </c>
-      <c r="C750" s="1" t="s">
-        <v>422</v>
+    <row r="751" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A751" s="1" t="s">
+        <v>749</v>
+      </c>
+      <c r="B751" s="1" t="s">
+        <v>812</v>
+      </c>
+      <c r="C751" s="1" t="s">
+        <v>421</v>
       </c>
     </row>
     <row r="752" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A752" s="1" t="s">
-        <v>749</v>
+        <v>750</v>
       </c>
       <c r="B752" s="1" t="s">
         <v>812</v>
@@ -11343,7 +11876,7 @@
     </row>
     <row r="753" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A753" s="1" t="s">
-        <v>750</v>
+        <v>751</v>
       </c>
       <c r="B753" s="1" t="s">
         <v>812</v>
@@ -11354,7 +11887,7 @@
     </row>
     <row r="754" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A754" s="1" t="s">
-        <v>751</v>
+        <v>752</v>
       </c>
       <c r="B754" s="1" t="s">
         <v>812</v>
@@ -11365,7 +11898,7 @@
     </row>
     <row r="755" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A755" s="1" t="s">
-        <v>752</v>
+        <v>753</v>
       </c>
       <c r="B755" s="1" t="s">
         <v>812</v>
@@ -11376,7 +11909,7 @@
     </row>
     <row r="756" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A756" s="1" t="s">
-        <v>753</v>
+        <v>754</v>
       </c>
       <c r="B756" s="1" t="s">
         <v>812</v>
@@ -11387,7 +11920,7 @@
     </row>
     <row r="757" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A757" s="1" t="s">
-        <v>754</v>
+        <v>755</v>
       </c>
       <c r="B757" s="1" t="s">
         <v>812</v>
@@ -11398,7 +11931,7 @@
     </row>
     <row r="758" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A758" s="1" t="s">
-        <v>755</v>
+        <v>756</v>
       </c>
       <c r="B758" s="1" t="s">
         <v>812</v>
@@ -11409,7 +11942,7 @@
     </row>
     <row r="759" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A759" s="1" t="s">
-        <v>756</v>
+        <v>757</v>
       </c>
       <c r="B759" s="1" t="s">
         <v>812</v>
@@ -11420,7 +11953,7 @@
     </row>
     <row r="760" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A760" s="1" t="s">
-        <v>757</v>
+        <v>758</v>
       </c>
       <c r="B760" s="1" t="s">
         <v>812</v>
@@ -11431,7 +11964,7 @@
     </row>
     <row r="761" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A761" s="1" t="s">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="B761" s="1" t="s">
         <v>812</v>
@@ -11442,7 +11975,7 @@
     </row>
     <row r="762" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A762" s="1" t="s">
-        <v>759</v>
+        <v>760</v>
       </c>
       <c r="B762" s="1" t="s">
         <v>812</v>
@@ -11453,7 +11986,7 @@
     </row>
     <row r="763" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A763" s="1" t="s">
-        <v>760</v>
+        <v>761</v>
       </c>
       <c r="B763" s="1" t="s">
         <v>812</v>
@@ -11464,7 +11997,7 @@
     </row>
     <row r="764" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A764" s="1" t="s">
-        <v>761</v>
+        <v>762</v>
       </c>
       <c r="B764" s="1" t="s">
         <v>812</v>
@@ -11475,7 +12008,7 @@
     </row>
     <row r="765" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A765" s="1" t="s">
-        <v>762</v>
+        <v>763</v>
       </c>
       <c r="B765" s="1" t="s">
         <v>812</v>
@@ -11486,7 +12019,7 @@
     </row>
     <row r="766" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A766" s="1" t="s">
-        <v>763</v>
+        <v>764</v>
       </c>
       <c r="B766" s="1" t="s">
         <v>812</v>
@@ -11497,7 +12030,7 @@
     </row>
     <row r="767" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A767" s="1" t="s">
-        <v>764</v>
+        <v>765</v>
       </c>
       <c r="B767" s="1" t="s">
         <v>812</v>
@@ -11508,7 +12041,7 @@
     </row>
     <row r="768" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A768" s="1" t="s">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="B768" s="1" t="s">
         <v>812</v>
@@ -11519,7 +12052,7 @@
     </row>
     <row r="769" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A769" s="1" t="s">
-        <v>766</v>
+        <v>767</v>
       </c>
       <c r="B769" s="1" t="s">
         <v>812</v>
@@ -11530,7 +12063,7 @@
     </row>
     <row r="770" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A770" s="1" t="s">
-        <v>767</v>
+        <v>768</v>
       </c>
       <c r="B770" s="1" t="s">
         <v>812</v>
@@ -11541,7 +12074,7 @@
     </row>
     <row r="771" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A771" s="1" t="s">
-        <v>768</v>
+        <v>769</v>
       </c>
       <c r="B771" s="1" t="s">
         <v>812</v>
@@ -11552,7 +12085,7 @@
     </row>
     <row r="772" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A772" s="1" t="s">
-        <v>769</v>
+        <v>770</v>
       </c>
       <c r="B772" s="1" t="s">
         <v>812</v>
@@ -11563,7 +12096,7 @@
     </row>
     <row r="773" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A773" s="1" t="s">
-        <v>770</v>
+        <v>771</v>
       </c>
       <c r="B773" s="1" t="s">
         <v>812</v>
@@ -11574,7 +12107,7 @@
     </row>
     <row r="774" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A774" s="1" t="s">
-        <v>771</v>
+        <v>772</v>
       </c>
       <c r="B774" s="1" t="s">
         <v>812</v>
@@ -11585,7 +12118,7 @@
     </row>
     <row r="775" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A775" s="1" t="s">
-        <v>772</v>
+        <v>773</v>
       </c>
       <c r="B775" s="1" t="s">
         <v>812</v>
@@ -11596,7 +12129,7 @@
     </row>
     <row r="776" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A776" s="1" t="s">
-        <v>773</v>
+        <v>774</v>
       </c>
       <c r="B776" s="1" t="s">
         <v>812</v>
@@ -11607,7 +12140,7 @@
     </row>
     <row r="777" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A777" s="1" t="s">
-        <v>774</v>
+        <v>775</v>
       </c>
       <c r="B777" s="1" t="s">
         <v>812</v>
@@ -11618,7 +12151,7 @@
     </row>
     <row r="778" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A778" s="1" t="s">
-        <v>775</v>
+        <v>776</v>
       </c>
       <c r="B778" s="1" t="s">
         <v>812</v>
@@ -11629,7 +12162,7 @@
     </row>
     <row r="779" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A779" s="1" t="s">
-        <v>776</v>
+        <v>777</v>
       </c>
       <c r="B779" s="1" t="s">
         <v>812</v>
@@ -11640,7 +12173,7 @@
     </row>
     <row r="780" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A780" s="1" t="s">
-        <v>777</v>
+        <v>778</v>
       </c>
       <c r="B780" s="1" t="s">
         <v>812</v>
@@ -11651,7 +12184,7 @@
     </row>
     <row r="781" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A781" s="1" t="s">
-        <v>778</v>
+        <v>779</v>
       </c>
       <c r="B781" s="1" t="s">
         <v>812</v>
@@ -11662,7 +12195,7 @@
     </row>
     <row r="782" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A782" s="1" t="s">
-        <v>779</v>
+        <v>780</v>
       </c>
       <c r="B782" s="1" t="s">
         <v>812</v>
@@ -11673,7 +12206,7 @@
     </row>
     <row r="783" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A783" s="1" t="s">
-        <v>780</v>
+        <v>781</v>
       </c>
       <c r="B783" s="1" t="s">
         <v>812</v>
@@ -11684,7 +12217,7 @@
     </row>
     <row r="784" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A784" s="1" t="s">
-        <v>781</v>
+        <v>782</v>
       </c>
       <c r="B784" s="1" t="s">
         <v>812</v>
@@ -11695,7 +12228,7 @@
     </row>
     <row r="785" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A785" s="1" t="s">
-        <v>782</v>
+        <v>783</v>
       </c>
       <c r="B785" s="1" t="s">
         <v>812</v>
@@ -11706,7 +12239,7 @@
     </row>
     <row r="786" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A786" s="1" t="s">
-        <v>783</v>
+        <v>784</v>
       </c>
       <c r="B786" s="1" t="s">
         <v>812</v>
@@ -11717,7 +12250,7 @@
     </row>
     <row r="787" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A787" s="1" t="s">
-        <v>784</v>
+        <v>785</v>
       </c>
       <c r="B787" s="1" t="s">
         <v>812</v>
@@ -11728,7 +12261,7 @@
     </row>
     <row r="788" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A788" s="1" t="s">
-        <v>785</v>
+        <v>786</v>
       </c>
       <c r="B788" s="1" t="s">
         <v>812</v>
@@ -11739,7 +12272,7 @@
     </row>
     <row r="789" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A789" s="1" t="s">
-        <v>786</v>
+        <v>787</v>
       </c>
       <c r="B789" s="1" t="s">
         <v>812</v>
@@ -11750,7 +12283,7 @@
     </row>
     <row r="790" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A790" s="1" t="s">
-        <v>787</v>
+        <v>788</v>
       </c>
       <c r="B790" s="1" t="s">
         <v>812</v>
@@ -11761,7 +12294,7 @@
     </row>
     <row r="791" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A791" s="1" t="s">
-        <v>788</v>
+        <v>789</v>
       </c>
       <c r="B791" s="1" t="s">
         <v>812</v>
@@ -11772,7 +12305,7 @@
     </row>
     <row r="792" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A792" s="1" t="s">
-        <v>789</v>
+        <v>790</v>
       </c>
       <c r="B792" s="1" t="s">
         <v>812</v>
@@ -11783,7 +12316,7 @@
     </row>
     <row r="793" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A793" s="1" t="s">
-        <v>790</v>
+        <v>791</v>
       </c>
       <c r="B793" s="1" t="s">
         <v>812</v>
@@ -11794,7 +12327,7 @@
     </row>
     <row r="794" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A794" s="1" t="s">
-        <v>791</v>
+        <v>792</v>
       </c>
       <c r="B794" s="1" t="s">
         <v>812</v>
@@ -11805,7 +12338,7 @@
     </row>
     <row r="795" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A795" s="1" t="s">
-        <v>792</v>
+        <v>793</v>
       </c>
       <c r="B795" s="1" t="s">
         <v>812</v>
@@ -11816,7 +12349,7 @@
     </row>
     <row r="796" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A796" s="1" t="s">
-        <v>793</v>
+        <v>794</v>
       </c>
       <c r="B796" s="1" t="s">
         <v>812</v>
@@ -11827,7 +12360,7 @@
     </row>
     <row r="797" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A797" s="1" t="s">
-        <v>794</v>
+        <v>795</v>
       </c>
       <c r="B797" s="1" t="s">
         <v>812</v>
@@ -11838,7 +12371,7 @@
     </row>
     <row r="798" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A798" s="1" t="s">
-        <v>795</v>
+        <v>797</v>
       </c>
       <c r="B798" s="1" t="s">
         <v>812</v>
@@ -11849,7 +12382,7 @@
     </row>
     <row r="799" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A799" s="1" t="s">
-        <v>796</v>
+        <v>798</v>
       </c>
       <c r="B799" s="1" t="s">
         <v>812</v>
@@ -11860,7 +12393,7 @@
     </row>
     <row r="800" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A800" s="1" t="s">
-        <v>797</v>
+        <v>799</v>
       </c>
       <c r="B800" s="1" t="s">
         <v>812</v>
@@ -11871,7 +12404,7 @@
     </row>
     <row r="801" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A801" s="1" t="s">
-        <v>798</v>
+        <v>800</v>
       </c>
       <c r="B801" s="1" t="s">
         <v>812</v>
@@ -11882,7 +12415,7 @@
     </row>
     <row r="802" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A802" s="1" t="s">
-        <v>799</v>
+        <v>801</v>
       </c>
       <c r="B802" s="1" t="s">
         <v>812</v>
@@ -11893,7 +12426,7 @@
     </row>
     <row r="803" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A803" s="1" t="s">
-        <v>800</v>
+        <v>802</v>
       </c>
       <c r="B803" s="1" t="s">
         <v>812</v>
@@ -11904,7 +12437,7 @@
     </row>
     <row r="804" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A804" s="1" t="s">
-        <v>801</v>
+        <v>803</v>
       </c>
       <c r="B804" s="1" t="s">
         <v>812</v>
@@ -11915,7 +12448,7 @@
     </row>
     <row r="805" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A805" s="1" t="s">
-        <v>802</v>
+        <v>804</v>
       </c>
       <c r="B805" s="1" t="s">
         <v>812</v>
@@ -11926,7 +12459,7 @@
     </row>
     <row r="806" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A806" s="1" t="s">
-        <v>803</v>
+        <v>805</v>
       </c>
       <c r="B806" s="1" t="s">
         <v>812</v>
@@ -11937,7 +12470,7 @@
     </row>
     <row r="807" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A807" s="1" t="s">
-        <v>804</v>
+        <v>806</v>
       </c>
       <c r="B807" s="1" t="s">
         <v>812</v>
@@ -11948,7 +12481,7 @@
     </row>
     <row r="808" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A808" s="1" t="s">
-        <v>805</v>
+        <v>807</v>
       </c>
       <c r="B808" s="1" t="s">
         <v>812</v>
@@ -11959,7 +12492,7 @@
     </row>
     <row r="809" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A809" s="1" t="s">
-        <v>806</v>
+        <v>808</v>
       </c>
       <c r="B809" s="1" t="s">
         <v>812</v>
@@ -11970,7 +12503,7 @@
     </row>
     <row r="810" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A810" s="1" t="s">
-        <v>807</v>
+        <v>809</v>
       </c>
       <c r="B810" s="1" t="s">
         <v>812</v>
@@ -11981,7 +12514,7 @@
     </row>
     <row r="811" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A811" s="1" t="s">
-        <v>808</v>
+        <v>810</v>
       </c>
       <c r="B811" s="1" t="s">
         <v>812</v>
@@ -11992,7 +12525,7 @@
     </row>
     <row r="812" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A812" s="1" t="s">
-        <v>809</v>
+        <v>811</v>
       </c>
       <c r="B812" s="1" t="s">
         <v>812</v>
@@ -12003,7 +12536,7 @@
     </row>
     <row r="813" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A813" s="1" t="s">
-        <v>810</v>
+        <v>796</v>
       </c>
       <c r="B813" s="1" t="s">
         <v>812</v>
@@ -12014,7 +12547,7 @@
     </row>
     <row r="814" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A814" s="1" t="s">
-        <v>811</v>
+        <v>813</v>
       </c>
       <c r="B814" s="1" t="s">
         <v>812</v>
@@ -12024,8 +12557,8 @@
       </c>
     </row>
     <row r="815" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A815" s="1" t="s">
-        <v>796</v>
+      <c r="A815" s="3" t="s">
+        <v>816</v>
       </c>
       <c r="B815" s="1" t="s">
         <v>812</v>
@@ -12035,8 +12568,8 @@
       </c>
     </row>
     <row r="816" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A816" s="1" t="s">
-        <v>813</v>
+      <c r="A816" s="3" t="s">
+        <v>814</v>
       </c>
       <c r="B816" s="1" t="s">
         <v>812</v>
@@ -12047,7 +12580,7 @@
     </row>
     <row r="817" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A817" s="3" t="s">
-        <v>816</v>
+        <v>815</v>
       </c>
       <c r="B817" s="1" t="s">
         <v>812</v>
@@ -12058,7 +12591,7 @@
     </row>
     <row r="818" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A818" s="3" t="s">
-        <v>814</v>
+        <v>817</v>
       </c>
       <c r="B818" s="1" t="s">
         <v>812</v>
@@ -12069,7 +12602,7 @@
     </row>
     <row r="819" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A819" s="3" t="s">
-        <v>815</v>
+        <v>818</v>
       </c>
       <c r="B819" s="1" t="s">
         <v>812</v>
@@ -12080,7 +12613,7 @@
     </row>
     <row r="820" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A820" s="3" t="s">
-        <v>817</v>
+        <v>819</v>
       </c>
       <c r="B820" s="1" t="s">
         <v>812</v>
@@ -12090,8 +12623,8 @@
       </c>
     </row>
     <row r="821" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A821" s="3" t="s">
-        <v>818</v>
+      <c r="A821" s="1" t="s">
+        <v>823</v>
       </c>
       <c r="B821" s="1" t="s">
         <v>812</v>
@@ -12102,7 +12635,7 @@
     </row>
     <row r="822" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A822" s="3" t="s">
-        <v>819</v>
+        <v>824</v>
       </c>
       <c r="B822" s="1" t="s">
         <v>812</v>
@@ -12112,8 +12645,8 @@
       </c>
     </row>
     <row r="823" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A823" s="1" t="s">
-        <v>823</v>
+      <c r="A823" s="3" t="s">
+        <v>825</v>
       </c>
       <c r="B823" s="1" t="s">
         <v>812</v>
@@ -12124,7 +12657,7 @@
     </row>
     <row r="824" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A824" s="3" t="s">
-        <v>824</v>
+        <v>826</v>
       </c>
       <c r="B824" s="1" t="s">
         <v>812</v>
@@ -12135,7 +12668,7 @@
     </row>
     <row r="825" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A825" s="3" t="s">
-        <v>825</v>
+        <v>827</v>
       </c>
       <c r="B825" s="1" t="s">
         <v>812</v>
@@ -12146,7 +12679,7 @@
     </row>
     <row r="826" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A826" s="3" t="s">
-        <v>826</v>
+        <v>828</v>
       </c>
       <c r="B826" s="1" t="s">
         <v>812</v>
@@ -12157,7 +12690,7 @@
     </row>
     <row r="827" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A827" s="3" t="s">
-        <v>827</v>
+        <v>829</v>
       </c>
       <c r="B827" s="1" t="s">
         <v>812</v>
@@ -12168,7 +12701,7 @@
     </row>
     <row r="828" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A828" s="3" t="s">
-        <v>828</v>
+        <v>830</v>
       </c>
       <c r="B828" s="1" t="s">
         <v>812</v>
@@ -12179,7 +12712,7 @@
     </row>
     <row r="829" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A829" s="3" t="s">
-        <v>829</v>
+        <v>831</v>
       </c>
       <c r="B829" s="1" t="s">
         <v>812</v>
@@ -12190,7 +12723,7 @@
     </row>
     <row r="830" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A830" s="3" t="s">
-        <v>830</v>
+        <v>832</v>
       </c>
       <c r="B830" s="1" t="s">
         <v>812</v>
@@ -12201,7 +12734,7 @@
     </row>
     <row r="831" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A831" s="3" t="s">
-        <v>831</v>
+        <v>833</v>
       </c>
       <c r="B831" s="1" t="s">
         <v>812</v>
@@ -12212,7 +12745,7 @@
     </row>
     <row r="832" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A832" s="3" t="s">
-        <v>832</v>
+        <v>834</v>
       </c>
       <c r="B832" s="1" t="s">
         <v>812</v>
@@ -12223,7 +12756,7 @@
     </row>
     <row r="833" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A833" s="3" t="s">
-        <v>833</v>
+        <v>835</v>
       </c>
       <c r="B833" s="1" t="s">
         <v>812</v>
@@ -12234,7 +12767,7 @@
     </row>
     <row r="834" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A834" s="3" t="s">
-        <v>834</v>
+        <v>836</v>
       </c>
       <c r="B834" s="1" t="s">
         <v>812</v>
@@ -12245,7 +12778,7 @@
     </row>
     <row r="835" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A835" s="3" t="s">
-        <v>835</v>
+        <v>837</v>
       </c>
       <c r="B835" s="1" t="s">
         <v>812</v>
@@ -12256,7 +12789,7 @@
     </row>
     <row r="836" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A836" s="3" t="s">
-        <v>836</v>
+        <v>838</v>
       </c>
       <c r="B836" s="1" t="s">
         <v>812</v>
@@ -12267,7 +12800,7 @@
     </row>
     <row r="837" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A837" s="3" t="s">
-        <v>837</v>
+        <v>839</v>
       </c>
       <c r="B837" s="1" t="s">
         <v>812</v>
@@ -12278,7 +12811,7 @@
     </row>
     <row r="838" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A838" s="3" t="s">
-        <v>838</v>
+        <v>840</v>
       </c>
       <c r="B838" s="1" t="s">
         <v>812</v>
@@ -12288,22 +12821,22 @@
       </c>
     </row>
     <row r="839" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A839" s="3" t="s">
-        <v>839</v>
+      <c r="A839" s="1" t="s">
+        <v>841</v>
       </c>
       <c r="B839" s="1" t="s">
-        <v>812</v>
+        <v>855</v>
       </c>
       <c r="C839" s="1" t="s">
         <v>421</v>
       </c>
     </row>
     <row r="840" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A840" s="3" t="s">
-        <v>840</v>
+      <c r="A840" s="1" t="s">
+        <v>842</v>
       </c>
       <c r="B840" s="1" t="s">
-        <v>812</v>
+        <v>855</v>
       </c>
       <c r="C840" s="1" t="s">
         <v>421</v>
@@ -12311,365 +12844,2169 @@
     </row>
     <row r="841" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A841" s="1" t="s">
-        <v>388</v>
+        <v>843</v>
       </c>
       <c r="B841" s="1" t="s">
         <v>855</v>
       </c>
       <c r="C841" s="1" t="s">
-        <v>855</v>
+        <v>421</v>
       </c>
     </row>
     <row r="842" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A842" s="1" t="s">
-        <v>841</v>
+        <v>850</v>
       </c>
       <c r="B842" s="1" t="s">
         <v>855</v>
       </c>
       <c r="C842" s="1" t="s">
-        <v>855</v>
+        <v>421</v>
       </c>
     </row>
     <row r="843" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A843" s="1" t="s">
-        <v>442</v>
+        <v>851</v>
       </c>
       <c r="B843" s="1" t="s">
         <v>855</v>
       </c>
       <c r="C843" s="1" t="s">
-        <v>855</v>
+        <v>421</v>
       </c>
     </row>
     <row r="844" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A844" s="1" t="s">
-        <v>842</v>
+        <v>852</v>
       </c>
       <c r="B844" s="1" t="s">
         <v>855</v>
       </c>
       <c r="C844" s="1" t="s">
-        <v>855</v>
+        <v>421</v>
       </c>
     </row>
     <row r="845" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A845" s="1" t="s">
-        <v>224</v>
+        <v>844</v>
       </c>
       <c r="B845" s="1" t="s">
         <v>855</v>
       </c>
       <c r="C845" s="1" t="s">
-        <v>855</v>
+        <v>421</v>
       </c>
     </row>
     <row r="846" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A846" s="1" t="s">
-        <v>843</v>
+        <v>845</v>
       </c>
       <c r="B846" s="1" t="s">
         <v>855</v>
       </c>
       <c r="C846" s="1" t="s">
-        <v>855</v>
+        <v>421</v>
       </c>
     </row>
     <row r="847" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A847" s="1" t="s">
-        <v>850</v>
+        <v>846</v>
       </c>
       <c r="B847" s="1" t="s">
         <v>855</v>
       </c>
       <c r="C847" s="1" t="s">
-        <v>855</v>
+        <v>421</v>
       </c>
     </row>
     <row r="848" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A848" s="1" t="s">
-        <v>851</v>
+        <v>853</v>
       </c>
       <c r="B848" s="1" t="s">
         <v>855</v>
       </c>
       <c r="C848" s="1" t="s">
-        <v>855</v>
+        <v>421</v>
       </c>
     </row>
     <row r="849" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A849" s="1" t="s">
-        <v>852</v>
+        <v>847</v>
       </c>
       <c r="B849" s="1" t="s">
         <v>855</v>
       </c>
       <c r="C849" s="1" t="s">
-        <v>855</v>
+        <v>421</v>
       </c>
     </row>
     <row r="850" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A850" s="1" t="s">
-        <v>844</v>
+        <v>848</v>
       </c>
       <c r="B850" s="1" t="s">
         <v>855</v>
       </c>
       <c r="C850" s="1" t="s">
-        <v>855</v>
+        <v>421</v>
       </c>
     </row>
     <row r="851" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A851" s="1" t="s">
-        <v>845</v>
+        <v>854</v>
       </c>
       <c r="B851" s="1" t="s">
         <v>855</v>
       </c>
       <c r="C851" s="1" t="s">
-        <v>855</v>
+        <v>421</v>
       </c>
     </row>
     <row r="852" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A852" s="1" t="s">
-        <v>846</v>
+        <v>849</v>
       </c>
       <c r="B852" s="1" t="s">
         <v>855</v>
       </c>
       <c r="C852" s="1" t="s">
-        <v>855</v>
+        <v>421</v>
       </c>
     </row>
     <row r="853" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A853" s="1" t="s">
-        <v>853</v>
+        <v>857</v>
       </c>
       <c r="B853" s="1" t="s">
         <v>855</v>
       </c>
       <c r="C853" s="1" t="s">
-        <v>855</v>
+        <v>421</v>
       </c>
     </row>
     <row r="854" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A854" s="1" t="s">
-        <v>847</v>
+        <v>856</v>
       </c>
       <c r="B854" s="1" t="s">
         <v>855</v>
       </c>
       <c r="C854" s="1" t="s">
-        <v>855</v>
+        <v>421</v>
       </c>
     </row>
     <row r="855" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A855" s="1" t="s">
-        <v>398</v>
+        <v>858</v>
       </c>
       <c r="B855" s="1" t="s">
         <v>855</v>
       </c>
       <c r="C855" s="1" t="s">
-        <v>855</v>
+        <v>421</v>
       </c>
     </row>
     <row r="856" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A856" s="1" t="s">
-        <v>848</v>
+        <v>859</v>
       </c>
       <c r="B856" s="1" t="s">
         <v>855</v>
       </c>
       <c r="C856" s="1" t="s">
-        <v>855</v>
+        <v>421</v>
       </c>
     </row>
     <row r="857" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A857" s="1" t="s">
-        <v>455</v>
+        <v>860</v>
       </c>
       <c r="B857" s="1" t="s">
         <v>855</v>
       </c>
       <c r="C857" s="1" t="s">
-        <v>855</v>
+        <v>421</v>
       </c>
     </row>
     <row r="858" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A858" s="1" t="s">
-        <v>454</v>
+        <v>861</v>
       </c>
       <c r="B858" s="1" t="s">
         <v>855</v>
       </c>
       <c r="C858" s="1" t="s">
-        <v>855</v>
+        <v>421</v>
       </c>
     </row>
     <row r="859" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A859" s="1" t="s">
-        <v>423</v>
+        <v>862</v>
       </c>
       <c r="B859" s="1" t="s">
         <v>855</v>
       </c>
       <c r="C859" s="1" t="s">
-        <v>855</v>
+        <v>421</v>
       </c>
     </row>
     <row r="860" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A860" s="1" t="s">
-        <v>854</v>
+        <v>863</v>
       </c>
       <c r="B860" s="1" t="s">
         <v>855</v>
       </c>
       <c r="C860" s="1" t="s">
-        <v>855</v>
+        <v>421</v>
       </c>
     </row>
     <row r="861" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A861" s="1" t="s">
-        <v>849</v>
+        <v>864</v>
       </c>
       <c r="B861" s="1" t="s">
         <v>855</v>
       </c>
       <c r="C861" s="1" t="s">
-        <v>855</v>
+        <v>421</v>
       </c>
     </row>
     <row r="862" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A862" s="1" t="s">
-        <v>857</v>
+        <v>865</v>
       </c>
       <c r="B862" s="1" t="s">
         <v>855</v>
       </c>
       <c r="C862" s="1" t="s">
-        <v>855</v>
+        <v>421</v>
       </c>
     </row>
     <row r="863" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A863" s="1" t="s">
-        <v>856</v>
+        <v>866</v>
       </c>
       <c r="B863" s="1" t="s">
         <v>855</v>
       </c>
       <c r="C863" s="1" t="s">
-        <v>855</v>
+        <v>421</v>
       </c>
     </row>
     <row r="864" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A864" s="1" t="s">
-        <v>858</v>
+        <v>867</v>
       </c>
       <c r="B864" s="1" t="s">
         <v>855</v>
       </c>
       <c r="C864" s="1" t="s">
-        <v>855</v>
-      </c>
-    </row>
-    <row r="865" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A865" s="1" t="s">
-        <v>859</v>
-      </c>
-      <c r="B865" s="1" t="s">
-        <v>855</v>
-      </c>
-      <c r="C865" s="1" t="s">
-        <v>855</v>
-      </c>
-    </row>
-    <row r="866" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A866" s="1" t="s">
-        <v>860</v>
-      </c>
-      <c r="B866" s="1" t="s">
-        <v>855</v>
-      </c>
-      <c r="C866" s="1" t="s">
-        <v>855</v>
-      </c>
-    </row>
-    <row r="867" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A867" s="1" t="s">
-        <v>861</v>
-      </c>
-      <c r="B867" s="1" t="s">
-        <v>855</v>
-      </c>
-      <c r="C867" s="1" t="s">
-        <v>855</v>
+        <v>421</v>
       </c>
     </row>
     <row r="868" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A868" s="1" t="s">
-        <v>862</v>
+        <v>868</v>
       </c>
       <c r="B868" s="1" t="s">
-        <v>855</v>
+        <v>812</v>
       </c>
       <c r="C868" s="1" t="s">
-        <v>855</v>
+        <v>1028</v>
       </c>
     </row>
     <row r="869" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A869" s="1" t="s">
-        <v>863</v>
+        <v>869</v>
       </c>
       <c r="B869" s="1" t="s">
-        <v>855</v>
+        <v>812</v>
       </c>
       <c r="C869" s="1" t="s">
-        <v>855</v>
+        <v>1028</v>
       </c>
     </row>
     <row r="870" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A870" s="1" t="s">
-        <v>864</v>
+        <v>870</v>
       </c>
       <c r="B870" s="1" t="s">
-        <v>855</v>
+        <v>812</v>
       </c>
       <c r="C870" s="1" t="s">
-        <v>855</v>
+        <v>1028</v>
       </c>
     </row>
     <row r="871" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A871" s="1" t="s">
-        <v>865</v>
+        <v>871</v>
       </c>
       <c r="B871" s="1" t="s">
-        <v>855</v>
+        <v>812</v>
       </c>
       <c r="C871" s="1" t="s">
-        <v>855</v>
+        <v>1028</v>
       </c>
     </row>
     <row r="872" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A872" s="1" t="s">
-        <v>866</v>
+        <v>872</v>
       </c>
       <c r="B872" s="1" t="s">
-        <v>855</v>
+        <v>421</v>
       </c>
       <c r="C872" s="1" t="s">
-        <v>855</v>
+        <v>1028</v>
       </c>
     </row>
     <row r="873" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A873" s="1" t="s">
-        <v>867</v>
+        <v>873</v>
       </c>
       <c r="B873" s="1" t="s">
-        <v>855</v>
+        <v>812</v>
       </c>
       <c r="C873" s="1" t="s">
-        <v>855</v>
+        <v>1028</v>
+      </c>
+    </row>
+    <row r="874" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A874" s="1" t="s">
+        <v>874</v>
+      </c>
+      <c r="B874" s="1" t="s">
+        <v>421</v>
+      </c>
+      <c r="C874" s="1" t="s">
+        <v>1028</v>
+      </c>
+    </row>
+    <row r="875" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A875" s="1" t="s">
+        <v>875</v>
+      </c>
+      <c r="B875" s="1" t="s">
+        <v>812</v>
+      </c>
+      <c r="C875" s="1" t="s">
+        <v>1028</v>
+      </c>
+    </row>
+    <row r="876" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A876" s="1" t="s">
+        <v>876</v>
+      </c>
+      <c r="B876" s="1" t="s">
+        <v>812</v>
+      </c>
+      <c r="C876" s="1" t="s">
+        <v>1028</v>
+      </c>
+    </row>
+    <row r="877" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A877" s="1" t="s">
+        <v>877</v>
+      </c>
+      <c r="B877" s="1" t="s">
+        <v>812</v>
+      </c>
+      <c r="C877" s="1" t="s">
+        <v>1028</v>
+      </c>
+    </row>
+    <row r="878" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A878" s="1" t="s">
+        <v>878</v>
+      </c>
+      <c r="B878" s="1" t="s">
+        <v>812</v>
+      </c>
+      <c r="C878" s="1" t="s">
+        <v>1028</v>
+      </c>
+    </row>
+    <row r="879" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A879" s="1" t="s">
+        <v>879</v>
+      </c>
+      <c r="B879" s="1" t="s">
+        <v>812</v>
+      </c>
+      <c r="C879" s="1" t="s">
+        <v>1028</v>
+      </c>
+    </row>
+    <row r="880" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A880" s="1" t="s">
+        <v>880</v>
+      </c>
+      <c r="B880" s="1" t="s">
+        <v>812</v>
+      </c>
+      <c r="C880" s="1" t="s">
+        <v>1028</v>
+      </c>
+    </row>
+    <row r="881" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A881" s="1" t="s">
+        <v>881</v>
+      </c>
+      <c r="B881" s="1" t="s">
+        <v>812</v>
+      </c>
+      <c r="C881" s="1" t="s">
+        <v>1028</v>
+      </c>
+    </row>
+    <row r="882" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A882" s="1" t="s">
+        <v>882</v>
+      </c>
+      <c r="B882" s="1" t="s">
+        <v>812</v>
+      </c>
+      <c r="C882" s="1" t="s">
+        <v>1028</v>
+      </c>
+    </row>
+    <row r="883" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A883" s="1" t="s">
+        <v>883</v>
+      </c>
+      <c r="B883" s="1" t="s">
+        <v>812</v>
+      </c>
+      <c r="C883" s="1" t="s">
+        <v>1028</v>
+      </c>
+    </row>
+    <row r="884" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A884" s="1" t="s">
+        <v>884</v>
+      </c>
+      <c r="B884" s="1" t="s">
+        <v>812</v>
+      </c>
+      <c r="C884" s="1" t="s">
+        <v>1028</v>
+      </c>
+    </row>
+    <row r="885" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A885" s="1" t="s">
+        <v>885</v>
+      </c>
+      <c r="B885" s="1" t="s">
+        <v>812</v>
+      </c>
+      <c r="C885" s="1" t="s">
+        <v>1028</v>
+      </c>
+    </row>
+    <row r="886" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A886" s="1" t="s">
+        <v>886</v>
+      </c>
+      <c r="B886" s="1" t="s">
+        <v>812</v>
+      </c>
+      <c r="C886" s="1" t="s">
+        <v>1028</v>
+      </c>
+    </row>
+    <row r="887" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A887" s="1" t="s">
+        <v>887</v>
+      </c>
+      <c r="B887" s="1" t="s">
+        <v>812</v>
+      </c>
+      <c r="C887" s="1" t="s">
+        <v>1028</v>
+      </c>
+    </row>
+    <row r="888" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A888" s="1" t="s">
+        <v>888</v>
+      </c>
+      <c r="B888" s="1" t="s">
+        <v>812</v>
+      </c>
+      <c r="C888" s="1" t="s">
+        <v>1028</v>
+      </c>
+    </row>
+    <row r="889" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A889" s="1" t="s">
+        <v>889</v>
+      </c>
+      <c r="B889" s="1" t="s">
+        <v>812</v>
+      </c>
+      <c r="C889" s="1" t="s">
+        <v>1028</v>
+      </c>
+    </row>
+    <row r="890" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A890" s="1" t="s">
+        <v>890</v>
+      </c>
+      <c r="B890" s="1" t="s">
+        <v>812</v>
+      </c>
+      <c r="C890" s="1" t="s">
+        <v>1028</v>
+      </c>
+    </row>
+    <row r="891" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A891" s="1" t="s">
+        <v>891</v>
+      </c>
+      <c r="B891" s="1" t="s">
+        <v>812</v>
+      </c>
+      <c r="C891" s="1" t="s">
+        <v>1028</v>
+      </c>
+    </row>
+    <row r="892" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A892" s="1" t="s">
+        <v>892</v>
+      </c>
+      <c r="B892" s="1" t="s">
+        <v>812</v>
+      </c>
+      <c r="C892" s="1" t="s">
+        <v>1028</v>
+      </c>
+    </row>
+    <row r="893" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A893" s="1" t="s">
+        <v>893</v>
+      </c>
+      <c r="B893" s="1" t="s">
+        <v>812</v>
+      </c>
+      <c r="C893" s="1" t="s">
+        <v>1028</v>
+      </c>
+    </row>
+    <row r="894" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A894" s="1" t="s">
+        <v>894</v>
+      </c>
+      <c r="B894" s="1" t="s">
+        <v>812</v>
+      </c>
+      <c r="C894" s="1" t="s">
+        <v>1028</v>
+      </c>
+    </row>
+    <row r="895" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A895" s="1" t="s">
+        <v>895</v>
+      </c>
+      <c r="B895" s="1" t="s">
+        <v>812</v>
+      </c>
+      <c r="C895" s="1" t="s">
+        <v>1028</v>
+      </c>
+    </row>
+    <row r="896" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A896" s="1" t="s">
+        <v>896</v>
+      </c>
+      <c r="B896" s="1" t="s">
+        <v>812</v>
+      </c>
+      <c r="C896" s="1" t="s">
+        <v>1028</v>
+      </c>
+    </row>
+    <row r="897" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A897" s="1" t="s">
+        <v>897</v>
+      </c>
+      <c r="B897" s="1" t="s">
+        <v>812</v>
+      </c>
+      <c r="C897" s="1" t="s">
+        <v>1028</v>
+      </c>
+    </row>
+    <row r="898" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A898" s="1" t="s">
+        <v>898</v>
+      </c>
+      <c r="B898" s="1" t="s">
+        <v>812</v>
+      </c>
+      <c r="C898" s="1" t="s">
+        <v>1028</v>
+      </c>
+    </row>
+    <row r="899" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A899" s="1" t="s">
+        <v>899</v>
+      </c>
+      <c r="B899" s="1" t="s">
+        <v>812</v>
+      </c>
+      <c r="C899" s="1" t="s">
+        <v>1028</v>
+      </c>
+    </row>
+    <row r="900" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A900" s="1" t="s">
+        <v>900</v>
+      </c>
+      <c r="B900" s="1" t="s">
+        <v>812</v>
+      </c>
+      <c r="C900" s="1" t="s">
+        <v>1028</v>
+      </c>
+    </row>
+    <row r="901" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A901" s="1" t="s">
+        <v>901</v>
+      </c>
+      <c r="B901" s="1" t="s">
+        <v>812</v>
+      </c>
+      <c r="C901" s="1" t="s">
+        <v>1028</v>
+      </c>
+    </row>
+    <row r="902" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A902" s="1" t="s">
+        <v>902</v>
+      </c>
+      <c r="B902" s="1" t="s">
+        <v>812</v>
+      </c>
+      <c r="C902" s="1" t="s">
+        <v>1028</v>
+      </c>
+    </row>
+    <row r="903" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A903" s="1" t="s">
+        <v>903</v>
+      </c>
+      <c r="B903" s="1" t="s">
+        <v>812</v>
+      </c>
+      <c r="C903" s="1" t="s">
+        <v>1028</v>
+      </c>
+    </row>
+    <row r="904" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A904" s="1" t="s">
+        <v>904</v>
+      </c>
+      <c r="B904" s="1" t="s">
+        <v>812</v>
+      </c>
+      <c r="C904" s="1" t="s">
+        <v>1028</v>
+      </c>
+    </row>
+    <row r="905" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A905" s="1" t="s">
+        <v>905</v>
+      </c>
+      <c r="B905" s="1" t="s">
+        <v>812</v>
+      </c>
+      <c r="C905" s="1" t="s">
+        <v>1028</v>
+      </c>
+    </row>
+    <row r="906" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A906" s="1" t="s">
+        <v>906</v>
+      </c>
+      <c r="B906" s="1" t="s">
+        <v>812</v>
+      </c>
+      <c r="C906" s="1" t="s">
+        <v>1028</v>
+      </c>
+    </row>
+    <row r="907" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A907" s="1" t="s">
+        <v>907</v>
+      </c>
+      <c r="B907" s="1" t="s">
+        <v>812</v>
+      </c>
+      <c r="C907" s="1" t="s">
+        <v>1028</v>
+      </c>
+    </row>
+    <row r="908" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A908" s="1" t="s">
+        <v>908</v>
+      </c>
+      <c r="B908" s="1" t="s">
+        <v>812</v>
+      </c>
+      <c r="C908" s="1" t="s">
+        <v>1028</v>
+      </c>
+    </row>
+    <row r="909" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A909" s="1" t="s">
+        <v>909</v>
+      </c>
+      <c r="B909" s="1" t="s">
+        <v>812</v>
+      </c>
+      <c r="C909" s="1" t="s">
+        <v>1028</v>
+      </c>
+    </row>
+    <row r="910" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A910" s="1" t="s">
+        <v>910</v>
+      </c>
+      <c r="B910" s="1" t="s">
+        <v>812</v>
+      </c>
+      <c r="C910" s="1" t="s">
+        <v>1028</v>
+      </c>
+    </row>
+    <row r="911" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A911" s="1" t="s">
+        <v>911</v>
+      </c>
+      <c r="B911" s="1" t="s">
+        <v>812</v>
+      </c>
+      <c r="C911" s="1" t="s">
+        <v>1028</v>
+      </c>
+    </row>
+    <row r="912" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A912" s="1" t="s">
+        <v>912</v>
+      </c>
+      <c r="B912" s="1" t="s">
+        <v>812</v>
+      </c>
+      <c r="C912" s="1" t="s">
+        <v>1028</v>
+      </c>
+    </row>
+    <row r="913" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A913" s="1" t="s">
+        <v>913</v>
+      </c>
+      <c r="B913" s="1" t="s">
+        <v>812</v>
+      </c>
+      <c r="C913" s="1" t="s">
+        <v>1028</v>
+      </c>
+    </row>
+    <row r="914" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A914" s="1" t="s">
+        <v>914</v>
+      </c>
+      <c r="B914" s="1" t="s">
+        <v>812</v>
+      </c>
+      <c r="C914" s="1" t="s">
+        <v>1028</v>
+      </c>
+    </row>
+    <row r="915" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A915" s="1" t="s">
+        <v>915</v>
+      </c>
+      <c r="B915" s="1" t="s">
+        <v>812</v>
+      </c>
+      <c r="C915" s="1" t="s">
+        <v>1028</v>
+      </c>
+    </row>
+    <row r="916" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A916" s="1" t="s">
+        <v>916</v>
+      </c>
+      <c r="B916" s="1" t="s">
+        <v>812</v>
+      </c>
+      <c r="C916" s="1" t="s">
+        <v>1028</v>
+      </c>
+    </row>
+    <row r="917" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A917" s="1" t="s">
+        <v>917</v>
+      </c>
+      <c r="B917" s="1" t="s">
+        <v>812</v>
+      </c>
+      <c r="C917" s="1" t="s">
+        <v>1028</v>
+      </c>
+    </row>
+    <row r="918" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A918" s="1" t="s">
+        <v>918</v>
+      </c>
+      <c r="B918" s="1" t="s">
+        <v>812</v>
+      </c>
+      <c r="C918" s="1" t="s">
+        <v>1028</v>
+      </c>
+    </row>
+    <row r="919" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A919" s="1" t="s">
+        <v>919</v>
+      </c>
+      <c r="B919" s="1" t="s">
+        <v>812</v>
+      </c>
+      <c r="C919" s="1" t="s">
+        <v>1028</v>
+      </c>
+    </row>
+    <row r="920" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A920" s="1" t="s">
+        <v>920</v>
+      </c>
+      <c r="B920" s="1" t="s">
+        <v>812</v>
+      </c>
+      <c r="C920" s="1" t="s">
+        <v>1028</v>
+      </c>
+    </row>
+    <row r="921" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A921" s="1" t="s">
+        <v>921</v>
+      </c>
+      <c r="B921" s="1" t="s">
+        <v>812</v>
+      </c>
+      <c r="C921" s="1" t="s">
+        <v>1028</v>
+      </c>
+    </row>
+    <row r="922" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A922" s="1" t="s">
+        <v>922</v>
+      </c>
+      <c r="B922" s="1" t="s">
+        <v>812</v>
+      </c>
+      <c r="C922" s="1" t="s">
+        <v>1028</v>
+      </c>
+    </row>
+    <row r="923" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A923" s="1" t="s">
+        <v>923</v>
+      </c>
+      <c r="B923" s="1" t="s">
+        <v>812</v>
+      </c>
+      <c r="C923" s="1" t="s">
+        <v>1028</v>
+      </c>
+    </row>
+    <row r="924" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A924" s="1" t="s">
+        <v>924</v>
+      </c>
+      <c r="B924" s="1" t="s">
+        <v>812</v>
+      </c>
+      <c r="C924" s="1" t="s">
+        <v>1028</v>
+      </c>
+    </row>
+    <row r="925" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A925" s="1" t="s">
+        <v>925</v>
+      </c>
+      <c r="B925" s="1" t="s">
+        <v>812</v>
+      </c>
+      <c r="C925" s="1" t="s">
+        <v>1028</v>
+      </c>
+    </row>
+    <row r="926" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A926" s="1" t="s">
+        <v>926</v>
+      </c>
+      <c r="B926" s="1" t="s">
+        <v>812</v>
+      </c>
+      <c r="C926" s="1" t="s">
+        <v>1028</v>
+      </c>
+    </row>
+    <row r="927" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A927" s="1" t="s">
+        <v>927</v>
+      </c>
+      <c r="B927" s="1" t="s">
+        <v>812</v>
+      </c>
+      <c r="C927" s="1" t="s">
+        <v>1028</v>
+      </c>
+    </row>
+    <row r="928" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A928" s="1" t="s">
+        <v>928</v>
+      </c>
+      <c r="B928" s="1" t="s">
+        <v>812</v>
+      </c>
+      <c r="C928" s="1" t="s">
+        <v>1028</v>
+      </c>
+    </row>
+    <row r="929" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A929" s="1" t="s">
+        <v>929</v>
+      </c>
+      <c r="B929" s="1" t="s">
+        <v>812</v>
+      </c>
+      <c r="C929" s="1" t="s">
+        <v>1028</v>
+      </c>
+    </row>
+    <row r="930" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A930" s="1" t="s">
+        <v>930</v>
+      </c>
+      <c r="B930" s="1" t="s">
+        <v>812</v>
+      </c>
+      <c r="C930" s="1" t="s">
+        <v>1028</v>
+      </c>
+    </row>
+    <row r="931" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A931" s="1" t="s">
+        <v>931</v>
+      </c>
+      <c r="B931" s="1" t="s">
+        <v>812</v>
+      </c>
+      <c r="C931" s="1" t="s">
+        <v>1028</v>
+      </c>
+    </row>
+    <row r="932" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A932" s="1" t="s">
+        <v>932</v>
+      </c>
+      <c r="B932" s="1" t="s">
+        <v>812</v>
+      </c>
+      <c r="C932" s="1" t="s">
+        <v>1028</v>
+      </c>
+    </row>
+    <row r="933" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A933" s="1" t="s">
+        <v>933</v>
+      </c>
+      <c r="B933" s="1" t="s">
+        <v>812</v>
+      </c>
+      <c r="C933" s="1" t="s">
+        <v>1028</v>
+      </c>
+    </row>
+    <row r="934" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A934" s="1" t="s">
+        <v>934</v>
+      </c>
+      <c r="B934" s="1" t="s">
+        <v>812</v>
+      </c>
+      <c r="C934" s="1" t="s">
+        <v>1028</v>
+      </c>
+    </row>
+    <row r="935" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A935" s="1" t="s">
+        <v>935</v>
+      </c>
+      <c r="B935" s="1" t="s">
+        <v>812</v>
+      </c>
+      <c r="C935" s="1" t="s">
+        <v>1028</v>
+      </c>
+    </row>
+    <row r="936" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A936" s="1" t="s">
+        <v>936</v>
+      </c>
+      <c r="B936" s="1" t="s">
+        <v>812</v>
+      </c>
+      <c r="C936" s="1" t="s">
+        <v>1028</v>
+      </c>
+    </row>
+    <row r="937" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A937" s="1" t="s">
+        <v>937</v>
+      </c>
+      <c r="B937" s="1" t="s">
+        <v>812</v>
+      </c>
+      <c r="C937" s="1" t="s">
+        <v>1028</v>
+      </c>
+    </row>
+    <row r="938" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A938" s="1" t="s">
+        <v>938</v>
+      </c>
+      <c r="B938" s="1" t="s">
+        <v>812</v>
+      </c>
+      <c r="C938" s="1" t="s">
+        <v>1028</v>
+      </c>
+    </row>
+    <row r="939" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A939" s="1" t="s">
+        <v>939</v>
+      </c>
+      <c r="B939" s="1" t="s">
+        <v>812</v>
+      </c>
+      <c r="C939" s="1" t="s">
+        <v>1028</v>
+      </c>
+    </row>
+    <row r="940" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A940" s="1" t="s">
+        <v>940</v>
+      </c>
+      <c r="B940" s="1" t="s">
+        <v>812</v>
+      </c>
+      <c r="C940" s="1" t="s">
+        <v>1028</v>
+      </c>
+    </row>
+    <row r="941" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A941" s="1" t="s">
+        <v>941</v>
+      </c>
+      <c r="B941" s="1" t="s">
+        <v>812</v>
+      </c>
+      <c r="C941" s="1" t="s">
+        <v>1028</v>
+      </c>
+    </row>
+    <row r="942" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A942" s="1" t="s">
+        <v>942</v>
+      </c>
+      <c r="B942" s="1" t="s">
+        <v>812</v>
+      </c>
+      <c r="C942" s="1" t="s">
+        <v>1028</v>
+      </c>
+    </row>
+    <row r="943" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A943" s="1" t="s">
+        <v>943</v>
+      </c>
+      <c r="B943" s="1" t="s">
+        <v>812</v>
+      </c>
+      <c r="C943" s="1" t="s">
+        <v>1028</v>
+      </c>
+    </row>
+    <row r="944" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A944" s="1" t="s">
+        <v>944</v>
+      </c>
+      <c r="B944" s="1" t="s">
+        <v>812</v>
+      </c>
+      <c r="C944" s="1" t="s">
+        <v>1028</v>
+      </c>
+    </row>
+    <row r="945" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A945" s="1" t="s">
+        <v>945</v>
+      </c>
+      <c r="B945" s="1" t="s">
+        <v>812</v>
+      </c>
+      <c r="C945" s="1" t="s">
+        <v>1028</v>
+      </c>
+    </row>
+    <row r="946" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A946" s="1" t="s">
+        <v>946</v>
+      </c>
+      <c r="B946" s="1" t="s">
+        <v>812</v>
+      </c>
+      <c r="C946" s="1" t="s">
+        <v>1028</v>
+      </c>
+    </row>
+    <row r="947" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A947" s="1" t="s">
+        <v>947</v>
+      </c>
+      <c r="B947" s="1" t="s">
+        <v>812</v>
+      </c>
+      <c r="C947" s="1" t="s">
+        <v>1028</v>
+      </c>
+    </row>
+    <row r="948" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A948" s="1" t="s">
+        <v>948</v>
+      </c>
+      <c r="B948" s="1" t="s">
+        <v>812</v>
+      </c>
+      <c r="C948" s="1" t="s">
+        <v>1028</v>
+      </c>
+    </row>
+    <row r="949" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A949" s="1" t="s">
+        <v>949</v>
+      </c>
+      <c r="B949" s="1" t="s">
+        <v>812</v>
+      </c>
+      <c r="C949" s="1" t="s">
+        <v>1028</v>
+      </c>
+    </row>
+    <row r="950" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A950" s="1" t="s">
+        <v>950</v>
+      </c>
+      <c r="B950" s="1" t="s">
+        <v>812</v>
+      </c>
+      <c r="C950" s="1" t="s">
+        <v>1028</v>
+      </c>
+    </row>
+    <row r="951" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A951" s="1" t="s">
+        <v>951</v>
+      </c>
+      <c r="B951" s="1" t="s">
+        <v>812</v>
+      </c>
+      <c r="C951" s="1" t="s">
+        <v>1028</v>
+      </c>
+    </row>
+    <row r="952" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A952" s="1" t="s">
+        <v>952</v>
+      </c>
+      <c r="B952" s="1" t="s">
+        <v>812</v>
+      </c>
+      <c r="C952" s="1" t="s">
+        <v>1028</v>
+      </c>
+    </row>
+    <row r="953" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A953" s="1" t="s">
+        <v>953</v>
+      </c>
+      <c r="B953" s="1" t="s">
+        <v>812</v>
+      </c>
+      <c r="C953" s="1" t="s">
+        <v>1028</v>
+      </c>
+    </row>
+    <row r="954" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A954" s="1" t="s">
+        <v>954</v>
+      </c>
+      <c r="B954" s="1" t="s">
+        <v>812</v>
+      </c>
+      <c r="C954" s="1" t="s">
+        <v>1028</v>
+      </c>
+    </row>
+    <row r="955" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A955" s="1" t="s">
+        <v>955</v>
+      </c>
+      <c r="B955" s="1" t="s">
+        <v>812</v>
+      </c>
+      <c r="C955" s="1" t="s">
+        <v>1028</v>
+      </c>
+    </row>
+    <row r="956" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A956" s="1" t="s">
+        <v>956</v>
+      </c>
+      <c r="B956" s="1" t="s">
+        <v>812</v>
+      </c>
+      <c r="C956" s="1" t="s">
+        <v>1028</v>
+      </c>
+    </row>
+    <row r="957" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A957" s="1" t="s">
+        <v>957</v>
+      </c>
+      <c r="B957" s="1" t="s">
+        <v>812</v>
+      </c>
+      <c r="C957" s="1" t="s">
+        <v>1028</v>
+      </c>
+    </row>
+    <row r="958" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A958" s="1" t="s">
+        <v>958</v>
+      </c>
+      <c r="B958" s="1" t="s">
+        <v>812</v>
+      </c>
+      <c r="C958" s="1" t="s">
+        <v>1028</v>
+      </c>
+    </row>
+    <row r="959" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A959" s="1" t="s">
+        <v>959</v>
+      </c>
+      <c r="B959" s="1" t="s">
+        <v>812</v>
+      </c>
+      <c r="C959" s="1" t="s">
+        <v>1028</v>
+      </c>
+    </row>
+    <row r="960" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A960" s="1" t="s">
+        <v>960</v>
+      </c>
+      <c r="B960" s="1" t="s">
+        <v>812</v>
+      </c>
+      <c r="C960" s="1" t="s">
+        <v>1028</v>
+      </c>
+    </row>
+    <row r="961" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A961" s="1" t="s">
+        <v>961</v>
+      </c>
+      <c r="B961" s="1" t="s">
+        <v>812</v>
+      </c>
+      <c r="C961" s="1" t="s">
+        <v>1028</v>
+      </c>
+    </row>
+    <row r="962" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A962" s="1" t="s">
+        <v>962</v>
+      </c>
+      <c r="B962" s="1" t="s">
+        <v>812</v>
+      </c>
+      <c r="C962" s="1" t="s">
+        <v>1028</v>
+      </c>
+    </row>
+    <row r="963" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A963" s="1" t="s">
+        <v>963</v>
+      </c>
+      <c r="B963" s="1" t="s">
+        <v>812</v>
+      </c>
+      <c r="C963" s="1" t="s">
+        <v>1028</v>
+      </c>
+    </row>
+    <row r="964" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A964" s="1" t="s">
+        <v>964</v>
+      </c>
+      <c r="B964" s="1" t="s">
+        <v>812</v>
+      </c>
+      <c r="C964" s="1" t="s">
+        <v>1028</v>
+      </c>
+    </row>
+    <row r="965" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A965" s="1" t="s">
+        <v>965</v>
+      </c>
+      <c r="B965" s="1" t="s">
+        <v>812</v>
+      </c>
+      <c r="C965" s="1" t="s">
+        <v>1028</v>
+      </c>
+    </row>
+    <row r="966" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A966" s="1" t="s">
+        <v>966</v>
+      </c>
+      <c r="B966" s="1" t="s">
+        <v>812</v>
+      </c>
+      <c r="C966" s="1" t="s">
+        <v>1028</v>
+      </c>
+    </row>
+    <row r="967" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A967" s="1" t="s">
+        <v>967</v>
+      </c>
+      <c r="B967" s="1" t="s">
+        <v>812</v>
+      </c>
+      <c r="C967" s="1" t="s">
+        <v>1028</v>
+      </c>
+    </row>
+    <row r="968" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A968" s="1" t="s">
+        <v>968</v>
+      </c>
+      <c r="B968" s="1" t="s">
+        <v>812</v>
+      </c>
+      <c r="C968" s="1" t="s">
+        <v>1028</v>
+      </c>
+    </row>
+    <row r="969" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A969" s="1" t="s">
+        <v>969</v>
+      </c>
+      <c r="B969" s="1" t="s">
+        <v>812</v>
+      </c>
+      <c r="C969" s="1" t="s">
+        <v>1028</v>
+      </c>
+    </row>
+    <row r="970" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A970" s="1" t="s">
+        <v>970</v>
+      </c>
+      <c r="B970" s="1" t="s">
+        <v>812</v>
+      </c>
+      <c r="C970" s="1" t="s">
+        <v>1028</v>
+      </c>
+    </row>
+    <row r="971" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A971" s="1" t="s">
+        <v>971</v>
+      </c>
+      <c r="B971" s="1" t="s">
+        <v>812</v>
+      </c>
+      <c r="C971" s="1" t="s">
+        <v>1028</v>
+      </c>
+    </row>
+    <row r="972" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A972" s="1" t="s">
+        <v>972</v>
+      </c>
+      <c r="B972" s="1" t="s">
+        <v>812</v>
+      </c>
+      <c r="C972" s="1" t="s">
+        <v>1028</v>
+      </c>
+    </row>
+    <row r="973" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A973" s="1" t="s">
+        <v>973</v>
+      </c>
+      <c r="B973" s="1" t="s">
+        <v>812</v>
+      </c>
+      <c r="C973" s="1" t="s">
+        <v>1028</v>
+      </c>
+    </row>
+    <row r="974" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A974" s="1" t="s">
+        <v>974</v>
+      </c>
+      <c r="B974" s="1" t="s">
+        <v>812</v>
+      </c>
+      <c r="C974" s="1" t="s">
+        <v>1028</v>
+      </c>
+    </row>
+    <row r="975" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A975" s="1" t="s">
+        <v>975</v>
+      </c>
+      <c r="B975" s="1" t="s">
+        <v>812</v>
+      </c>
+      <c r="C975" s="1" t="s">
+        <v>1028</v>
+      </c>
+    </row>
+    <row r="976" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A976" s="1" t="s">
+        <v>976</v>
+      </c>
+      <c r="B976" s="1" t="s">
+        <v>812</v>
+      </c>
+      <c r="C976" s="1" t="s">
+        <v>1028</v>
+      </c>
+    </row>
+    <row r="977" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A977" s="1" t="s">
+        <v>977</v>
+      </c>
+      <c r="B977" s="1" t="s">
+        <v>812</v>
+      </c>
+      <c r="C977" s="1" t="s">
+        <v>1028</v>
+      </c>
+    </row>
+    <row r="978" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A978" s="1" t="s">
+        <v>978</v>
+      </c>
+      <c r="B978" s="1" t="s">
+        <v>812</v>
+      </c>
+      <c r="C978" s="1" t="s">
+        <v>1028</v>
+      </c>
+    </row>
+    <row r="979" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A979" s="1" t="s">
+        <v>979</v>
+      </c>
+      <c r="B979" s="1" t="s">
+        <v>812</v>
+      </c>
+      <c r="C979" s="1" t="s">
+        <v>1028</v>
+      </c>
+    </row>
+    <row r="980" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A980" s="1" t="s">
+        <v>980</v>
+      </c>
+      <c r="B980" s="1" t="s">
+        <v>812</v>
+      </c>
+      <c r="C980" s="1" t="s">
+        <v>1028</v>
+      </c>
+    </row>
+    <row r="981" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A981" s="1" t="s">
+        <v>981</v>
+      </c>
+      <c r="B981" s="1" t="s">
+        <v>812</v>
+      </c>
+      <c r="C981" s="1" t="s">
+        <v>1028</v>
+      </c>
+    </row>
+    <row r="982" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A982" s="1" t="s">
+        <v>982</v>
+      </c>
+      <c r="B982" s="1" t="s">
+        <v>812</v>
+      </c>
+      <c r="C982" s="1" t="s">
+        <v>1028</v>
+      </c>
+    </row>
+    <row r="983" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A983" s="1" t="s">
+        <v>983</v>
+      </c>
+      <c r="B983" s="1" t="s">
+        <v>812</v>
+      </c>
+      <c r="C983" s="1" t="s">
+        <v>1028</v>
+      </c>
+    </row>
+    <row r="984" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A984" s="1" t="s">
+        <v>984</v>
+      </c>
+      <c r="B984" s="1" t="s">
+        <v>812</v>
+      </c>
+      <c r="C984" s="1" t="s">
+        <v>1028</v>
+      </c>
+    </row>
+    <row r="985" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A985" s="1" t="s">
+        <v>985</v>
+      </c>
+      <c r="B985" s="1" t="s">
+        <v>812</v>
+      </c>
+      <c r="C985" s="1" t="s">
+        <v>1028</v>
+      </c>
+    </row>
+    <row r="986" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A986" s="1" t="s">
+        <v>986</v>
+      </c>
+      <c r="B986" s="1" t="s">
+        <v>812</v>
+      </c>
+      <c r="C986" s="1" t="s">
+        <v>1028</v>
+      </c>
+    </row>
+    <row r="987" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A987" s="1" t="s">
+        <v>987</v>
+      </c>
+      <c r="B987" s="1" t="s">
+        <v>812</v>
+      </c>
+      <c r="C987" s="1" t="s">
+        <v>1028</v>
+      </c>
+    </row>
+    <row r="988" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A988" s="1" t="s">
+        <v>988</v>
+      </c>
+      <c r="B988" s="1" t="s">
+        <v>812</v>
+      </c>
+      <c r="C988" s="1" t="s">
+        <v>1028</v>
+      </c>
+    </row>
+    <row r="989" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A989" s="1" t="s">
+        <v>989</v>
+      </c>
+      <c r="B989" s="1" t="s">
+        <v>812</v>
+      </c>
+      <c r="C989" s="1" t="s">
+        <v>1028</v>
+      </c>
+    </row>
+    <row r="990" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A990" s="1" t="s">
+        <v>990</v>
+      </c>
+      <c r="B990" s="1" t="s">
+        <v>812</v>
+      </c>
+      <c r="C990" s="1" t="s">
+        <v>1028</v>
+      </c>
+    </row>
+    <row r="991" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A991" s="1" t="s">
+        <v>991</v>
+      </c>
+      <c r="B991" s="1" t="s">
+        <v>812</v>
+      </c>
+      <c r="C991" s="1" t="s">
+        <v>1028</v>
+      </c>
+    </row>
+    <row r="992" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A992" s="1" t="s">
+        <v>992</v>
+      </c>
+      <c r="B992" s="1" t="s">
+        <v>421</v>
+      </c>
+      <c r="C992" s="1" t="s">
+        <v>1028</v>
+      </c>
+    </row>
+    <row r="993" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A993" s="1" t="s">
+        <v>993</v>
+      </c>
+      <c r="B993" s="1" t="s">
+        <v>812</v>
+      </c>
+      <c r="C993" s="1" t="s">
+        <v>1028</v>
+      </c>
+    </row>
+    <row r="994" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A994" s="1" t="s">
+        <v>994</v>
+      </c>
+      <c r="B994" s="1" t="s">
+        <v>812</v>
+      </c>
+      <c r="C994" s="1" t="s">
+        <v>1028</v>
+      </c>
+    </row>
+    <row r="995" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A995" s="1" t="s">
+        <v>995</v>
+      </c>
+      <c r="B995" s="1" t="s">
+        <v>812</v>
+      </c>
+      <c r="C995" s="1" t="s">
+        <v>1028</v>
+      </c>
+    </row>
+    <row r="996" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A996" s="1" t="s">
+        <v>996</v>
+      </c>
+      <c r="B996" s="1" t="s">
+        <v>812</v>
+      </c>
+      <c r="C996" s="1" t="s">
+        <v>1028</v>
+      </c>
+    </row>
+    <row r="997" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A997" s="1" t="s">
+        <v>997</v>
+      </c>
+      <c r="B997" s="1" t="s">
+        <v>812</v>
+      </c>
+      <c r="C997" s="1" t="s">
+        <v>1028</v>
+      </c>
+    </row>
+    <row r="998" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A998" s="1" t="s">
+        <v>998</v>
+      </c>
+      <c r="B998" s="1" t="s">
+        <v>812</v>
+      </c>
+      <c r="C998" s="1" t="s">
+        <v>1028</v>
+      </c>
+    </row>
+    <row r="999" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A999" s="1" t="s">
+        <v>999</v>
+      </c>
+      <c r="B999" s="1" t="s">
+        <v>812</v>
+      </c>
+      <c r="C999" s="1" t="s">
+        <v>1028</v>
+      </c>
+    </row>
+    <row r="1000" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1000" s="1" t="s">
+        <v>1000</v>
+      </c>
+      <c r="B1000" s="1" t="s">
+        <v>812</v>
+      </c>
+      <c r="C1000" s="1" t="s">
+        <v>1028</v>
+      </c>
+    </row>
+    <row r="1002" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1002" s="1" t="s">
+        <v>1001</v>
+      </c>
+      <c r="B1002" s="1" t="s">
+        <v>812</v>
+      </c>
+      <c r="C1002" s="1" t="s">
+        <v>1028</v>
+      </c>
+    </row>
+    <row r="1003" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1003" s="1" t="s">
+        <v>1002</v>
+      </c>
+      <c r="B1003" s="1" t="s">
+        <v>812</v>
+      </c>
+      <c r="C1003" s="1" t="s">
+        <v>1028</v>
+      </c>
+    </row>
+    <row r="1004" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1004" s="1" t="s">
+        <v>1003</v>
+      </c>
+      <c r="B1004" s="1" t="s">
+        <v>812</v>
+      </c>
+      <c r="C1004" s="1" t="s">
+        <v>1028</v>
+      </c>
+    </row>
+    <row r="1005" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1005" s="1" t="s">
+        <v>1004</v>
+      </c>
+      <c r="B1005" s="1" t="s">
+        <v>812</v>
+      </c>
+      <c r="C1005" s="1" t="s">
+        <v>1028</v>
+      </c>
+    </row>
+    <row r="1006" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1006" s="1" t="s">
+        <v>1005</v>
+      </c>
+      <c r="B1006" s="1" t="s">
+        <v>812</v>
+      </c>
+      <c r="C1006" s="1" t="s">
+        <v>1028</v>
+      </c>
+    </row>
+    <row r="1007" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1007" s="1" t="s">
+        <v>1006</v>
+      </c>
+      <c r="B1007" s="1" t="s">
+        <v>812</v>
+      </c>
+      <c r="C1007" s="1" t="s">
+        <v>1028</v>
+      </c>
+    </row>
+    <row r="1008" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1008" s="1" t="s">
+        <v>1007</v>
+      </c>
+      <c r="B1008" s="1" t="s">
+        <v>421</v>
+      </c>
+      <c r="C1008" s="1" t="s">
+        <v>1028</v>
+      </c>
+    </row>
+    <row r="1009" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1009" s="1" t="s">
+        <v>1008</v>
+      </c>
+      <c r="B1009" s="1" t="s">
+        <v>812</v>
+      </c>
+      <c r="C1009" s="1" t="s">
+        <v>1028</v>
+      </c>
+    </row>
+    <row r="1010" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1010" s="1" t="s">
+        <v>1009</v>
+      </c>
+      <c r="B1010" s="1" t="s">
+        <v>812</v>
+      </c>
+      <c r="C1010" s="1" t="s">
+        <v>1028</v>
+      </c>
+    </row>
+    <row r="1011" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1011" s="1" t="s">
+        <v>1010</v>
+      </c>
+      <c r="B1011" s="1" t="s">
+        <v>812</v>
+      </c>
+      <c r="C1011" s="1" t="s">
+        <v>1028</v>
+      </c>
+    </row>
+    <row r="1012" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1012" s="1" t="s">
+        <v>1011</v>
+      </c>
+      <c r="B1012" s="1" t="s">
+        <v>421</v>
+      </c>
+      <c r="C1012" s="1" t="s">
+        <v>1028</v>
+      </c>
+    </row>
+    <row r="1013" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1013" s="1" t="s">
+        <v>1012</v>
+      </c>
+      <c r="B1013" s="1" t="s">
+        <v>421</v>
+      </c>
+      <c r="C1013" s="1" t="s">
+        <v>1028</v>
+      </c>
+    </row>
+    <row r="1014" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1014" s="1" t="s">
+        <v>1013</v>
+      </c>
+      <c r="B1014" s="1" t="s">
+        <v>421</v>
+      </c>
+      <c r="C1014" s="1" t="s">
+        <v>1028</v>
+      </c>
+    </row>
+    <row r="1015" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1015" s="1" t="s">
+        <v>1014</v>
+      </c>
+      <c r="B1015" s="1" t="s">
+        <v>812</v>
+      </c>
+      <c r="C1015" s="1" t="s">
+        <v>1028</v>
+      </c>
+    </row>
+    <row r="1016" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1016" s="1" t="s">
+        <v>1015</v>
+      </c>
+      <c r="B1016" s="1" t="s">
+        <v>812</v>
+      </c>
+      <c r="C1016" s="1" t="s">
+        <v>1028</v>
+      </c>
+    </row>
+    <row r="1017" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1017" s="1" t="s">
+        <v>1016</v>
+      </c>
+      <c r="B1017" s="1" t="s">
+        <v>812</v>
+      </c>
+      <c r="C1017" s="1" t="s">
+        <v>1028</v>
+      </c>
+    </row>
+    <row r="1018" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1018" s="1" t="s">
+        <v>1017</v>
+      </c>
+      <c r="B1018" s="1" t="s">
+        <v>421</v>
+      </c>
+      <c r="C1018" s="1" t="s">
+        <v>1028</v>
+      </c>
+    </row>
+    <row r="1019" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1019" s="1" t="s">
+        <v>1018</v>
+      </c>
+      <c r="B1019" s="1" t="s">
+        <v>812</v>
+      </c>
+      <c r="C1019" s="1" t="s">
+        <v>1028</v>
+      </c>
+    </row>
+    <row r="1020" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1020" s="1" t="s">
+        <v>1019</v>
+      </c>
+      <c r="B1020" s="1" t="s">
+        <v>812</v>
+      </c>
+      <c r="C1020" s="1" t="s">
+        <v>1028</v>
+      </c>
+    </row>
+    <row r="1021" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1021" s="1" t="s">
+        <v>1020</v>
+      </c>
+      <c r="B1021" s="1" t="s">
+        <v>812</v>
+      </c>
+      <c r="C1021" s="1" t="s">
+        <v>1028</v>
+      </c>
+    </row>
+    <row r="1022" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1022" s="1" t="s">
+        <v>1021</v>
+      </c>
+      <c r="B1022" s="1" t="s">
+        <v>812</v>
+      </c>
+      <c r="C1022" s="1" t="s">
+        <v>1028</v>
+      </c>
+    </row>
+    <row r="1023" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1023" s="1" t="s">
+        <v>1022</v>
+      </c>
+      <c r="B1023" s="1" t="s">
+        <v>812</v>
+      </c>
+      <c r="C1023" s="1" t="s">
+        <v>1028</v>
+      </c>
+    </row>
+    <row r="1024" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1024" s="1" t="s">
+        <v>1023</v>
+      </c>
+      <c r="B1024" s="1" t="s">
+        <v>812</v>
+      </c>
+      <c r="C1024" s="1" t="s">
+        <v>1028</v>
+      </c>
+    </row>
+    <row r="1025" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1025" s="1" t="s">
+        <v>1024</v>
+      </c>
+      <c r="B1025" s="1" t="s">
+        <v>812</v>
+      </c>
+      <c r="C1025" s="1" t="s">
+        <v>1028</v>
+      </c>
+    </row>
+    <row r="1026" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1026" s="1" t="s">
+        <v>1025</v>
+      </c>
+      <c r="B1026" s="1" t="s">
+        <v>812</v>
+      </c>
+      <c r="C1026" s="1" t="s">
+        <v>1028</v>
+      </c>
+    </row>
+    <row r="1027" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1027" s="1" t="s">
+        <v>1026</v>
+      </c>
+      <c r="B1027" s="1" t="s">
+        <v>812</v>
+      </c>
+      <c r="C1027" s="1" t="s">
+        <v>1028</v>
+      </c>
+    </row>
+    <row r="1028" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1028" s="1" t="s">
+        <v>1027</v>
+      </c>
+      <c r="B1028" s="1" t="s">
+        <v>812</v>
+      </c>
+      <c r="C1028" s="1" t="s">
+        <v>1028</v>
+      </c>
+    </row>
+    <row r="1029" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1029" s="1" t="s">
+        <v>1029</v>
+      </c>
+      <c r="B1029" s="1" t="s">
+        <v>812</v>
+      </c>
+      <c r="C1029" s="1" t="s">
+        <v>421</v>
+      </c>
+    </row>
+    <row r="1030" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1030" s="6" t="s">
+        <v>1030</v>
+      </c>
+      <c r="B1030" s="1" t="s">
+        <v>812</v>
+      </c>
+      <c r="C1030" s="1" t="s">
+        <v>421</v>
+      </c>
+    </row>
+    <row r="1031" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1031" s="1" t="s">
+        <v>1031</v>
+      </c>
+      <c r="B1031" s="1" t="s">
+        <v>812</v>
+      </c>
+      <c r="C1031" s="1" t="s">
+        <v>421</v>
+      </c>
+    </row>
+    <row r="1032" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1032" s="1" t="s">
+        <v>1032</v>
+      </c>
+      <c r="B1032" s="1" t="s">
+        <v>812</v>
+      </c>
+      <c r="C1032" s="1" t="s">
+        <v>421</v>
+      </c>
+    </row>
+    <row r="1033" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1033" s="1" t="s">
+        <v>1035</v>
+      </c>
+      <c r="B1033" s="1" t="s">
+        <v>812</v>
+      </c>
+      <c r="C1033" s="1" t="s">
+        <v>421</v>
+      </c>
+    </row>
+    <row r="1034" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1034" s="1" t="s">
+        <v>1034</v>
+      </c>
+      <c r="B1034" s="1" t="s">
+        <v>812</v>
+      </c>
+      <c r="C1034" s="1" t="s">
+        <v>421</v>
+      </c>
+    </row>
+    <row r="1035" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1035" s="1" t="s">
+        <v>1033</v>
+      </c>
+      <c r="B1035" s="1" t="s">
+        <v>812</v>
+      </c>
+      <c r="C1035" s="1" t="s">
+        <v>421</v>
+      </c>
+    </row>
+    <row r="1036" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1036" s="1" t="s">
+        <v>1036</v>
+      </c>
+      <c r="B1036" s="1" t="s">
+        <v>812</v>
+      </c>
+      <c r="C1036" s="1" t="s">
+        <v>421</v>
+      </c>
+    </row>
+    <row r="1037" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1037" s="1" t="s">
+        <v>1037</v>
+      </c>
+      <c r="B1037" s="1" t="s">
+        <v>812</v>
+      </c>
+      <c r="C1037" s="1" t="s">
+        <v>421</v>
+      </c>
+    </row>
+    <row r="1038" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1038" s="1" t="s">
+        <v>1038</v>
+      </c>
+      <c r="B1038" s="1" t="s">
+        <v>812</v>
+      </c>
+      <c r="C1038" s="1" t="s">
+        <v>421</v>
+      </c>
+    </row>
+    <row r="1039" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1039" s="1" t="s">
+        <v>1039</v>
+      </c>
+      <c r="B1039" s="1" t="s">
+        <v>812</v>
+      </c>
+      <c r="C1039" s="1" t="s">
+        <v>421</v>
+      </c>
+    </row>
+    <row r="1040" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1040" s="1" t="s">
+        <v>1040</v>
+      </c>
+      <c r="B1040" s="1" t="s">
+        <v>812</v>
+      </c>
+      <c r="C1040" s="1" t="s">
+        <v>421</v>
+      </c>
+    </row>
+    <row r="1041" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1041" s="1" t="s">
+        <v>1041</v>
+      </c>
+      <c r="B1041" s="1" t="s">
+        <v>812</v>
+      </c>
+      <c r="C1041" s="1" t="s">
+        <v>421</v>
       </c>
     </row>
   </sheetData>
@@ -12677,13 +15014,16 @@
     <sortCondition ref="A1:A226"/>
   </sortState>
   <conditionalFormatting sqref="A1:A1048576">
-    <cfRule type="duplicateValues" dxfId="2" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="3" priority="1"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A895:A1048576 A1:A739">
-    <cfRule type="duplicateValues" dxfId="1" priority="3"/>
+  <conditionalFormatting sqref="A1889:A1048576 A1:A739">
+    <cfRule type="duplicateValues" dxfId="2" priority="4"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D831:D836">
-    <cfRule type="duplicateValues" dxfId="0" priority="2"/>
+  <conditionalFormatting sqref="A1889:A1048576 A1:A866">
+    <cfRule type="duplicateValues" dxfId="1" priority="2"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D829:D834">
+    <cfRule type="duplicateValues" dxfId="0" priority="3"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
